--- a/EXCEL/Data/køn.xlsx
+++ b/EXCEL/Data/køn.xlsx
@@ -100,7 +100,7 @@
     <t>Datasæt 02 2016</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 12.46.33</t>
+    <t>Kørsel 8.4.2026 13.56.21</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
